--- a/responsables_acciones_de_gracia.xlsx
+++ b/responsables_acciones_de_gracia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafa_\Documents\Dropbox\Cristiano\Acciones de gracias\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafa_\Documents\Dropbox\Cristiano\Acciones de gracias\mi-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4633143-6548-43A8-AEEB-B7DE01ADB9FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8701AE-8582-4607-81C1-9B114556275C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{FDDC7848-536F-4369-9C8D-360041AD8D6B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDDC7848-536F-4369-9C8D-360041AD8D6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="47">
   <si>
     <t>Responsables</t>
   </si>
@@ -144,9 +144,6 @@
   </si>
   <si>
     <t>Yuiner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gio </t>
   </si>
   <si>
     <t>Vicente</t>
@@ -661,7 +658,7 @@
         <v>10</v>
       </c>
       <c r="E5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -681,7 +678,7 @@
         <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
         <v>28</v>
@@ -690,7 +687,7 @@
         <v>21</v>
       </c>
       <c r="I6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -710,7 +707,7 @@
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G7" t="s">
         <v>21</v>
@@ -727,7 +724,7 @@
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" t="s">
         <v>13</v>
@@ -770,10 +767,10 @@
         <v>7</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F10" t="s">
         <v>25</v>
@@ -793,7 +790,7 @@
         <v>8</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
         <v>13</v>
@@ -822,7 +819,7 @@
         <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G12" t="s">
         <v>24</v>
@@ -851,7 +848,7 @@
         <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I13" t="s">
         <v>25</v>
@@ -886,13 +883,13 @@
         <v>23</v>
       </c>
       <c r="I14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" t="s">
         <v>43</v>
       </c>
-      <c r="J14" t="s">
-        <v>44</v>
-      </c>
       <c r="K14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -912,7 +909,7 @@
         <v>30</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G15" t="s">
         <v>22</v>
@@ -941,13 +938,13 @@
         <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -990,7 +987,7 @@
         <v>11</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E18" t="s">
         <v>13</v>
@@ -999,7 +996,7 @@
         <v>22</v>
       </c>
       <c r="G18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H18" t="s">
         <v>22</v>
@@ -1008,7 +1005,7 @@
         <v>23</v>
       </c>
       <c r="J18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K18" t="s">
         <v>12</v>
@@ -1199,22 +1196,22 @@
         <v>24</v>
       </c>
       <c r="F25" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="G25" t="s">
         <v>21</v>
       </c>
       <c r="H25" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" t="s">
         <v>36</v>
       </c>
-      <c r="I25" t="s">
-        <v>37</v>
-      </c>
       <c r="J25" t="s">
+        <v>35</v>
+      </c>
+      <c r="K25" t="s">
         <v>36</v>
-      </c>
-      <c r="K25" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">

--- a/responsables_acciones_de_gracia.xlsx
+++ b/responsables_acciones_de_gracia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafa_\Documents\Dropbox\Cristiano\Acciones de gracias\mi-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8701AE-8582-4607-81C1-9B114556275C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55631EB-D899-4A3D-B1C8-A60ACA230B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDDC7848-536F-4369-9C8D-360041AD8D6B}"/>
   </bookViews>
@@ -572,8 +572,8 @@
     <col min="3" max="3" width="14.140625" customWidth="1"/>
     <col min="4" max="4" width="16.5703125" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.140625" customWidth="1"/>
     <col min="9" max="9" width="10.42578125" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
@@ -657,7 +657,7 @@
       <c r="C5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D5" t="s">
         <v>41</v>
       </c>
     </row>

--- a/responsables_acciones_de_gracia.xlsx
+++ b/responsables_acciones_de_gracia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafa_\Documents\Dropbox\Cristiano\Acciones de gracias\mi-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C55631EB-D899-4A3D-B1C8-A60ACA230B37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D74DD5-1416-4BCB-9B3F-9AF0BAE10B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDDC7848-536F-4369-9C8D-360041AD8D6B}"/>
   </bookViews>

--- a/responsables_acciones_de_gracia.xlsx
+++ b/responsables_acciones_de_gracia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafa_\Documents\Dropbox\Cristiano\Acciones de gracias\mi-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D74DD5-1416-4BCB-9B3F-9AF0BAE10B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE8849D-535D-45BB-99F0-42FA4B55BF61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDDC7848-536F-4369-9C8D-360041AD8D6B}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="46">
   <si>
     <t>Responsables</t>
   </si>
@@ -177,9 +177,6 @@
   </si>
   <si>
     <t>Mauricio</t>
-  </si>
-  <si>
-    <t>Victor</t>
   </si>
 </sst>
 </file>
@@ -566,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A6215FD-5B2B-4D07-A46B-99C54472F7AB}">
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="14.140625" customWidth="1"/>
@@ -616,668 +613,526 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
       </c>
+      <c r="D2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
+      <c r="D3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B4">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
       </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>41</v>
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="H6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I6" t="s">
-        <v>46</v>
+        <v>42</v>
+      </c>
+      <c r="J6" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J8" t="s">
         <v>40</v>
-      </c>
-      <c r="E8" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
+        <v>9</v>
+      </c>
+      <c r="B9">
+        <v>2025</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s">
         <v>12</v>
       </c>
-      <c r="B9">
-        <v>2024</v>
-      </c>
-      <c r="C9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>14</v>
-      </c>
       <c r="F9" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G9" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="H9" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>2025</v>
       </c>
       <c r="C10" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D10" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>38</v>
+      </c>
+      <c r="H10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B11">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B12">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B13">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
       </c>
       <c r="E13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" t="s">
         <v>13</v>
       </c>
-      <c r="F13" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" t="s">
-        <v>14</v>
-      </c>
       <c r="H13" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="I13" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J13" t="s">
-        <v>28</v>
+        <v>34</v>
+      </c>
+      <c r="K13" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B14">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" t="s">
         <v>16</v>
       </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" t="s">
         <v>28</v>
-      </c>
-      <c r="G14" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" t="s">
-        <v>43</v>
-      </c>
-      <c r="K14" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B15">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E15" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="F15" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>22</v>
+        <v>12</v>
+      </c>
+      <c r="H15" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" t="s">
+        <v>14</v>
+      </c>
+      <c r="K15" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B16">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C16" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" t="s">
         <v>13</v>
       </c>
-      <c r="E16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" t="s">
-        <v>24</v>
-      </c>
       <c r="G16" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="J16" t="s">
-        <v>40</v>
+        <v>22</v>
+      </c>
+      <c r="K16" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B17">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H17" t="s">
-        <v>29</v>
+        <v>35</v>
+      </c>
+      <c r="I17" t="s">
+        <v>36</v>
       </c>
       <c r="J17" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="K17" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B18">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E18" t="s">
         <v>13</v>
       </c>
       <c r="F18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G18" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="H18" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="I18" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J18" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="K18" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B19">
         <v>2026</v>
       </c>
       <c r="C19" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>2</v>
-      </c>
-      <c r="B20">
-        <v>2026</v>
-      </c>
-      <c r="C20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G19" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>3</v>
-      </c>
-      <c r="B21">
-        <v>2026</v>
-      </c>
-      <c r="C21" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" t="s">
-        <v>21</v>
-      </c>
-      <c r="G21" t="s">
-        <v>13</v>
-      </c>
-      <c r="H21" t="s">
-        <v>29</v>
-      </c>
-      <c r="I21" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" t="s">
-        <v>34</v>
-      </c>
-      <c r="K21" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22">
-        <v>4</v>
-      </c>
-      <c r="B22">
-        <v>2026</v>
-      </c>
-      <c r="C22" t="s">
-        <v>10</v>
-      </c>
-      <c r="D22" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" t="s">
-        <v>16</v>
-      </c>
-      <c r="G22" t="s">
-        <v>24</v>
-      </c>
-      <c r="H22" t="s">
+      <c r="H19" t="s">
         <v>25</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J19" t="s">
         <v>14</v>
       </c>
-      <c r="J22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>5</v>
-      </c>
-      <c r="B23">
-        <v>2026</v>
-      </c>
-      <c r="C23" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" t="s">
-        <v>12</v>
-      </c>
-      <c r="H23" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23" t="s">
-        <v>14</v>
-      </c>
-      <c r="K23" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24">
-        <v>6</v>
-      </c>
-      <c r="B24">
-        <v>2026</v>
-      </c>
-      <c r="C24" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" t="s">
-        <v>13</v>
-      </c>
-      <c r="G24" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24" t="s">
-        <v>22</v>
-      </c>
-      <c r="K24" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>7</v>
-      </c>
-      <c r="B25">
-        <v>2026</v>
-      </c>
-      <c r="C25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" t="s">
-        <v>24</v>
-      </c>
-      <c r="F25" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" t="s">
-        <v>35</v>
-      </c>
-      <c r="I25" t="s">
-        <v>36</v>
-      </c>
-      <c r="J25" t="s">
-        <v>35</v>
-      </c>
-      <c r="K25" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26">
-        <v>8</v>
-      </c>
-      <c r="B26">
-        <v>2026</v>
-      </c>
-      <c r="C26" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" t="s">
-        <v>33</v>
-      </c>
-      <c r="E26" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" t="s">
-        <v>21</v>
-      </c>
-      <c r="G26" t="s">
-        <v>12</v>
-      </c>
-      <c r="H26" t="s">
-        <v>34</v>
-      </c>
-      <c r="I26" t="s">
-        <v>29</v>
-      </c>
-      <c r="J26" t="s">
-        <v>34</v>
-      </c>
-      <c r="K26" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>9</v>
-      </c>
-      <c r="B27">
-        <v>2026</v>
-      </c>
-      <c r="C27" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27" t="s">
-        <v>12</v>
-      </c>
-      <c r="H27" t="s">
-        <v>25</v>
-      </c>
-      <c r="J27" t="s">
-        <v>14</v>
-      </c>
-      <c r="K27" t="s">
+      <c r="K19" t="s">
         <v>28</v>
       </c>
     </row>

--- a/responsables_acciones_de_gracia.xlsx
+++ b/responsables_acciones_de_gracia.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafa_\Documents\Dropbox\Cristiano\Acciones de gracias\mi-dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FE8849D-535D-45BB-99F0-42FA4B55BF61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{101D3106-F985-4CE6-B488-25C1276B0DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDDC7848-536F-4369-9C8D-360041AD8D6B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$K$19</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -1137,6 +1140,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K19" xr:uid="{6A6215FD-5B2B-4D07-A46B-99C54472F7AB}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
